--- a/outputs/03_Driver_Schedule_generated.xlsx
+++ b/outputs/03_Driver_Schedule_generated.xlsx
@@ -606,7 +606,11 @@
           <t>HOT Beef Stroganoff → Dinner</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
@@ -640,7 +644,11 @@
           <t>HOT Falafels → Lunch (Veg)</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
@@ -674,7 +682,11 @@
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
           <t>GC → Rex</t>
@@ -708,7 +720,11 @@
           <t>HOT Jerk Chicken → Dinner</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>1.5 hotels</t>
+        </is>
+      </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
@@ -780,7 +796,11 @@
           <t>HOT Beef Nacho Mix → Lunch</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
@@ -814,7 +834,11 @@
           <t>HOT Vegan Nacho Mix → Lunch (Veg)</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0.5 hotels</t>
+        </is>
+      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
@@ -848,7 +872,11 @@
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
           <t>GC → Rex</t>
@@ -882,7 +910,11 @@
           <t>HOT Pork/Chicken/Halal Carnitas → Dinner</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr"/>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
@@ -954,7 +986,11 @@
           <t>HOT Crispy Chicken Tenders → Lunch</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
@@ -988,7 +1024,11 @@
           <t>HOT Vegan Tenders → Lunch (Veg)</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr"/>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0.5 hotels</t>
+        </is>
+      </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
@@ -1022,7 +1062,11 @@
           <t>Cold Chiffonade Lettuce &amp; Sliced Peppers → Lunch (wraps)</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
           <t>LAN → Rex</t>
@@ -1056,7 +1100,11 @@
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
           <t>GC → Rex</t>
@@ -1242,7 +1290,11 @@
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr"/>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
           <t>GC → Rex</t>
@@ -1394,7 +1446,11 @@
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr"/>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
           <t>GC → Rex</t>
@@ -1506,7 +1562,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>2 hotels</t>
+          <t>3 hotels</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -1582,7 +1638,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1 hotel</t>
+          <t>0.5 hotel</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -1618,7 +1674,11 @@
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr"/>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
           <t>GC → Rex</t>
@@ -1728,7 +1788,11 @@
           <t>HOT Carrot Cabbage Fry → Dinner side</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr"/>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
           <t>LAN → Rex</t>
@@ -1762,7 +1826,11 @@
           <t>HOT Rice → Dinner</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr"/>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
@@ -2022,7 +2090,11 @@
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
           <t>GC → Rex</t>
@@ -2212,7 +2284,11 @@
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr"/>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
           <t>GC → Rex</t>
@@ -2322,7 +2398,11 @@
           <t>HOT Rice → Dinner</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
@@ -2356,7 +2436,11 @@
           <t>HOT Green Beans → Dinner side</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr"/>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
@@ -2466,7 +2550,11 @@
           <t>HOT Steamed Rice → Dinner</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
@@ -2500,7 +2588,11 @@
           <t>HOT Broccoli → Dinner side</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr"/>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
           <t>LAN → Rex</t>
@@ -2534,7 +2626,11 @@
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr"/>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
           <t>GC → Rex</t>
@@ -2644,7 +2740,11 @@
           <t>HOT Coconut Rice &amp; Peas → Dinner</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr"/>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
           <t>LAN → Rex</t>
@@ -2678,7 +2778,11 @@
           <t>HOT Eggplant/Cassava Stew → Dinner</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
@@ -3658,7 +3762,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>50 pcs</t>
+          <t>2 hotels</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3694,7 +3798,11 @@
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
           <t>GC → Rex</t>
@@ -3956,7 +4064,11 @@
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr"/>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
           <t>GC → Rex</t>
@@ -4144,7 +4256,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>155 pcs</t>
+          <t>4 hotels</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4218,7 +4330,11 @@
           <t>Cold Chiffonade Lettuce &amp; Sliced Peppers → Lunch (wraps)</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr"/>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
           <t>LAN → Rex</t>
@@ -4252,7 +4368,11 @@
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr"/>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
           <t>GC → Rex</t>
@@ -4552,7 +4672,11 @@
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr"/>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
           <t>GC → Rex</t>
@@ -4588,7 +4712,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>2.5 hotels</t>
+          <t>3 hotels</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -4662,7 +4786,11 @@
           <t>HOT Chakalaka → Dinner side</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr"/>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
           <t>LAN → Rex</t>
@@ -4776,7 +4904,11 @@
           <t>HOT Vegan/No-Soy Mushroom Fried Rice → Dinner (Veg)</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr"/>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
@@ -4810,7 +4942,11 @@
           <t>HOT Spring Rolls → Dinner side</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr"/>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
@@ -4920,7 +5056,11 @@
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="E42" s="3" t="inlineStr"/>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
           <t>GC → Rex</t>
@@ -4954,7 +5094,11 @@
           <t>Pick up Pepperoni + Veg Pizza at vendor</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr"/>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
           <t>Vendor → Rex</t>
@@ -5034,7 +5178,11 @@
           <t>HOT Potato Wedges → Dinner</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr"/>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
@@ -5324,7 +5472,11 @@
           <t>HOT Pasta + Broccoli &amp; Carrot → Dinner</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>9 hotels</t>
+        </is>
+      </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
@@ -5438,7 +5590,11 @@
           <t>HOT Curry Fish → Dinner</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr"/>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
@@ -5472,7 +5628,11 @@
           <t>HOT Curry Spiced Tofu → Dinner (Veg)</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>0.5 hotels</t>
+        </is>
+      </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
@@ -5506,7 +5666,11 @@
           <t>HOT Green Curry Sauce → Dinner</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr"/>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
@@ -5540,7 +5704,11 @@
           <t>HOT Rice + Green Beans → Dinner</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>7 hotels</t>
+        </is>
+      </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
           <t>LAN → Rex</t>
@@ -5764,7 +5932,11 @@
           <t>HOT BBQ Chicken Legs → Dinner</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr"/>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
@@ -5798,7 +5970,11 @@
           <t>HOT BBQ Vegan Tenders → Dinner (Veg)</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr"/>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>0.5 hotels</t>
+        </is>
+      </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
@@ -5832,7 +6008,11 @@
           <t>HOT Herb Garlic Potatoes → Dinner</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
@@ -5866,7 +6046,11 @@
           <t>HOT Peas &amp; Carrot → Dinner side</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr"/>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
           <t>LAN → Rex</t>
@@ -5976,7 +6160,11 @@
           <t>HOT Eggplant/Cassava Stew → Dinner</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
@@ -6010,7 +6198,11 @@
           <t>HOT Beef &amp; Vegetable Stew → Dinner</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr"/>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
@@ -6082,7 +6274,11 @@
           <t>HOT Halal Beef Burgers → Lunch</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
@@ -6230,7 +6426,11 @@
           <t>HOT Chow Mein + Nappa Cabbage → Dinner</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr"/>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>8 hotels</t>
+        </is>
+      </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
@@ -6388,7 +6588,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>0.5 unit</t>
+          <t>2 bins</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -6401,7 +6601,11 @@
           <t>LAN → Rex</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>⚠ CONFIRM 2 bins/4u — LAN → Rex</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -6462,7 +6666,11 @@
           <t>HOT Tandoori Tofu → Dinner (Veg)</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr"/>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>0.5 hotels</t>
+        </is>
+      </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
@@ -6496,7 +6704,11 @@
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr"/>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
           <t>GC → Rex</t>
@@ -6606,7 +6818,11 @@
           <t>HOT Beef Massaman Curry → Dinner</t>
         </is>
       </c>
-      <c r="E42" s="3" t="inlineStr"/>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
@@ -6640,7 +6856,11 @@
           <t>HOT Vegan Massaman Curry → Dinner (Veg)</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr"/>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>0.5 hotels</t>
+        </is>
+      </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
@@ -6674,7 +6894,11 @@
           <t>HOT Rice → Dinner side</t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr"/>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
@@ -6708,7 +6932,11 @@
           <t>Cold Broccoli Salad → NC Wk1 Sun Lunch</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr"/>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>

--- a/outputs/03_Driver_Schedule_generated.xlsx
+++ b/outputs/03_Driver_Schedule_generated.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1426,42 +1426,42 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>May 22</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>Pick up Baked Rolls at GC</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>pickup</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>No AM run — Bean Salad pre-sent Thu PM</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Cold salad already at Rex</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -1481,22 +1481,22 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>HOT Pork/Chicken/Halal + Veg Adobo → Dinner</t>
+          <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>3 hotels</t>
+          <t>pickup</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr"/>
@@ -1519,22 +1519,22 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>HOT Pineapple Rice → Dinner side</t>
+          <t>HOT Pork/Chicken/Halal + Veg Adobo → Dinner</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>4 hotels</t>
+          <t>3 hotels</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr"/>
@@ -1557,63 +1557,63 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
+          <t>HOT Pineapple Rice → Dinner side</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>May 22</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
           <t>HOT Green Beans → Dinner side</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>May 23</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>HOT CONC Salad Beef → Lunch</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr"/>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1633,63 +1633,63 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>HOT CONC Salad Beef → Lunch</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>May 23</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
           <t>HOT CONC Salad Vegan → Lunch (Veg)</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>0.5 hotel</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>May 23</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>Pick up Baked Rolls at GC</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>pickup</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -1709,22 +1709,22 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>HOT Gomen Besiga Beef → Dinner</t>
+          <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>80 lbs</t>
+          <t>pickup</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr"/>
@@ -1747,12 +1747,12 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>HOT Vegan Gomen Besiga → Dinner (Veg)</t>
+          <t>HOT Gomen Besiga Beef → Dinner</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>15 lbs</t>
+          <t>80 lbs</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -1785,22 +1785,22 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>HOT Carrot Cabbage Fry → Dinner side</t>
+          <t>HOT Vegan Gomen Besiga → Dinner (Veg)</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>2 hotels</t>
+          <t>15 lbs</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr"/>
@@ -1823,22 +1823,22 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>HOT Rice → Dinner</t>
+          <t>HOT Carrot Cabbage Fry → Dinner side</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>4 hotels</t>
+          <t>2 hotels</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>LAN → Rex</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>LAN → Rex</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr"/>
@@ -1861,25 +1861,63 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
+          <t>HOT Rice → Dinner</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>May 23</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
           <t>Cold Greens + Lettuce/Tomato → Sun Lunch</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="E38" s="3" t="inlineStr">
         <is>
           <t>3 bins + 1 bag</t>
         </is>
       </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
         <is>
           <t>fridge</t>
         </is>
@@ -1896,7 +1934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2608,78 +2646,78 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>May 26</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Cold Coronation Chicken Salad → Wed Lunch</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>May 27</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Pick up Baked Rolls at GC</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>pickup</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>May 27</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>HOT Yetisse Fish → Dinner</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>150 pcs</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr"/>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>No AM run — Coronation Chicken Salad pre-sent Tue PM</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Cold salad already at Rex</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -2699,22 +2737,22 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>HOT Spiced Tofu → Dinner (Veg)</t>
+          <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>50 pcs</t>
+          <t>pickup</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr"/>
@@ -2737,12 +2775,12 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>HOT Coconut Rice &amp; Peas → Dinner</t>
+          <t>HOT Yetisse Fish → Dinner</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>4 hotels</t>
+          <t>150 pcs</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -2775,22 +2813,22 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>HOT Eggplant/Cassava Stew → Dinner</t>
+          <t>HOT Spiced Tofu → Dinner (Veg)</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>2 hotels</t>
+          <t>50 pcs</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>LAN → Rex</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>LAN → Rex</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr"/>
@@ -2813,177 +2851,177 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
+          <t>HOT Coconut Rice &amp; Peas → Dinner</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>May 27</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>HOT Eggplant/Cassava Stew → Dinner</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>May 27</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
           <t>Cold Chickpea Salad → Thu Lunch</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>2 bins</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>May 28</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>AM</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>HOT Halal Beef Burgers → Lunch</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>160 pcs</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>May 28</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>AM</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>HOT Black Bean Patties → Lunch (Veg)</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>20 pcs</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>May 28</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>HOT Beef/Halal/Vegan Sausages → Dinner</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>250 pcs</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>May 28</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>HOT Mashed Potato → Dinner</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>80 lbs</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -3003,12 +3041,12 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>HOT Peas &amp; Carrot → Dinner side</t>
+          <t>HOT Beef/Halal/Vegan Sausages → Dinner</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>3 hotels</t>
+          <t>250 pcs</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -3041,12 +3079,12 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>HOT Gravy → Dinner</t>
+          <t>HOT Mashed Potato → Dinner</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>½ batch</t>
+          <t>80 lbs</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -3079,22 +3117,22 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Cold Chicken Ranch Mix → Fri Lunch</t>
+          <t>HOT Peas &amp; Carrot → Dinner side</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>2 bins</t>
+          <t>3 hotels</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr"/>
@@ -3117,139 +3155,139 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Cold Slaw → Fri Lunch side</t>
+          <t>HOT Gravy → Dinner</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
+          <t>½ batch</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>May 28</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Cold Chicken Ranch Mix → Fri Lunch</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
           <t>2 bins</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>May 29</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>HOT Crispy Falafel → Lunch (Veg)</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>0.5 hotel</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr"/>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>May 28</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Cold Slaw → Fri Lunch side</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>May 29</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>HOT Arroz con Pollo + Vegan Arroz → Dinner</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>100 lbs</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>May 29</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>HOT Refried Beans → Dinner side</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>HOT Crispy Falafel → Lunch (Veg)</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>0.5 hotel</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -3269,22 +3307,22 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Cold Tuna Rex Salad Mix → Sat Lunch</t>
+          <t>HOT Arroz con Pollo + Vegan Arroz → Dinner</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>2 bins</t>
+          <t>100 lbs</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr"/>
@@ -3292,12 +3330,12 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>May 30</t>
+          <t>May 29</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -3307,22 +3345,22 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>HOT Beef + Vegan Meatloaf → Dinner</t>
+          <t>HOT Refried Beans → Dinner side</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>8 trays</t>
+          <t>3 hotels</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr"/>
@@ -3330,78 +3368,78 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>May 29</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Cold Tuna Rex Salad Mix → Sat Lunch</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>May 30</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>HOT Roasted Potatoes → Dinner</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>May 30</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>HOT Butternut Squash → Dinner side</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>No AM run — Tuna Rex + Chickpea Rex Salad pre-sent Fri PM</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Cold salad already at Rex</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -3421,27 +3459,183 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
+          <t>HOT Beef + Vegan Meatloaf → Dinner</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>8 trays</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>May 30</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>HOT Roasted Potatoes → Dinner</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>May 30</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>HOT Butternut Squash → Dinner side</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>May 30</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
           <t>HOT Gravy → Dinner (Meatloaf)</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>½ batch</t>
         </is>
       </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
         <is>
           <t>Held from Thu batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>May 30</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Cold Broccoli Salad → Wk3 Sun Lunch</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>fridge</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4846,42 +5040,42 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>Jun 5</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>HOT Chicken &amp; Mushroom Fried Rice → Dinner</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>5 hotels</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>No AM run — Bean Salad pre-sent Thu PM</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Cold salad already at Rex</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -4901,12 +5095,12 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>HOT Vegan/No-Soy Mushroom Fried Rice → Dinner (Veg)</t>
+          <t>HOT Chicken &amp; Mushroom Fried Rice → Dinner</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>1 hotel</t>
+          <t>5 hotels</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -4939,63 +5133,63 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
+          <t>HOT Vegan/No-Soy Mushroom Fried Rice → Dinner (Veg)</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Jun 5</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
           <t>HOT Spring Rolls → Dinner side</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E40" s="3" t="inlineStr">
         <is>
           <t>2 hotels</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>Jun 6</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>HOT CONC Salad Beef → Lunch</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>80 lbs</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr"/>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -5015,63 +5209,63 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
+          <t>HOT CONC Salad Beef → Lunch</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>80 lbs</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Jun 6</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
           <t>HOT CONC Salad Vegan → Lunch (Veg)</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>12 lbs</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Jun 6</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>Pick up Baked Rolls at GC</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>pickup</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -5091,7 +5285,7 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Pick up Pepperoni + Veg Pizza at vendor</t>
+          <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -5101,19 +5295,15 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>Vendor → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>Vendor → Rex</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>Driver collects ordered pizza</t>
-        </is>
-      </c>
+          <t>GC → Rex</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -5133,27 +5323,27 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Cold Greens + Lettuce/Tomato → Sun Lunch</t>
+          <t>Pick up Pepperoni + Veg Pizza at vendor</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>3 bins + 1 bag</t>
+          <t>pickup</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Vendor → Rex</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Vendor → Rex</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>fridge</t>
+          <t>Driver collects ordered pizza</t>
         </is>
       </c>
     </row>
@@ -5175,25 +5365,67 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
+          <t>Cold Greens + Lettuce/Tomato → Sun Lunch</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>3 bins + 1 bag</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>fridge</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Jun 6</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
           <t>HOT Potato Wedges → Dinner</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="E46" s="3" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr"/>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5206,7 +5438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6066,78 +6298,78 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Jun 9</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Cold Coronation Chicken Salad → Wed Lunch</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Jun 10</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>HOT Vegan Pot Pie + Veg Medley → Dinner (Veg)</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>30 lbs</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Jun 10</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>HOT Roasted Potatoes → Dinner</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>No AM run — Coronation Chicken Salad pre-sent Tue PM</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Cold salad already at Rex</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -6157,12 +6389,12 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>HOT Eggplant/Cassava Stew → Dinner</t>
+          <t>HOT Vegan Pot Pie + Veg Medley → Dinner (Veg)</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>2 hotels</t>
+          <t>30 lbs</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -6195,12 +6427,12 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>HOT Beef &amp; Vegetable Stew → Dinner</t>
+          <t>HOT Roasted Potatoes → Dinner</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>3 hotels</t>
+          <t>4 hotels</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -6233,101 +6465,101 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
+          <t>HOT Eggplant/Cassava Stew → Dinner</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Jun 10</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>HOT Beef &amp; Vegetable Stew → Dinner</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Jun 10</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
           <t>Cold Chickpea Salad → Thu Lunch</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>2 bins</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Jun 11</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>HOT Halal Beef Burgers → Lunch</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Jun 11</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>HOT Black Bean Patties → Lunch (Veg)</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>20 pcs</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr"/>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6347,101 +6579,101 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>HOT Halal Beef Burgers → Lunch</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Jun 11</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>HOT Black Bean Patties → Lunch (Veg)</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>20 pcs</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Jun 11</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
           <t>Cold Lettuce / Tomato → Lunch</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>1 unit</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>Jun 11</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>HOT Teriyaki Chicken + Five-Spice Tofu → Dinner</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>215 pcs</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>Jun 11</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>HOT Chow Mein + Nappa Cabbage → Dinner</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>8 hotels</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -6461,12 +6693,12 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Cold Beef Nacho Mix → Rex fridge</t>
+          <t>HOT Teriyaki Chicken + Five-Spice Tofu → Dinner</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>80 lbs</t>
+          <t>215 pcs</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -6479,11 +6711,7 @@
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>Rex holds until Wk1 Mon AM pull</t>
-        </is>
-      </c>
+      <c r="H33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -6503,12 +6731,12 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Cold Vegan Nacho Mix → Rex fridge</t>
+          <t>HOT Chow Mein + Nappa Cabbage → Dinner</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>15 lbs</t>
+          <t>8 hotels</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -6521,11 +6749,7 @@
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>Rex holds until Wk1 Mon AM pull</t>
-        </is>
-      </c>
+      <c r="H34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -6545,25 +6769,29 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Cold Chicken Ranch Mix → Fri Lunch</t>
+          <t>Cold Beef Nacho Mix → Rex fridge</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>2 bins</t>
+          <t>80 lbs</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr"/>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Rex holds until Wk1 Mon AM pull</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -6583,143 +6811,147 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Cold Slaw → Fri Lunch side</t>
+          <t>Cold Vegan Nacho Mix → Rex fridge</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
+          <t>15 lbs</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Rex holds until Wk1 Mon AM pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Jun 11</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Cold Chicken Ranch Mix → Fri Lunch</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
           <t>2 bins</t>
         </is>
       </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>⚠ CONFIRM 2 bins/4u — LAN → Rex</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Jun 12</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>HOT Crispy Falafel → Lunch (Veg)</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>0.5 hotel</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr"/>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Jun 11</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Cold Slaw → Fri Lunch side</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>⚠ CONFIRM 2 bins/4u — LAN → Rex</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>Jun 12</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>HOT Tandoori Tofu → Dinner (Veg)</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>0.5 hotels</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>Jun 12</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>Pick up Baked Rolls at GC</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>pickup</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>HOT Crispy Falafel → Lunch (Veg)</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>0.5 hotel</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -6739,12 +6971,12 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>HOT Vegetable Biryani → Dinner</t>
+          <t>HOT Tandoori Tofu → Dinner (Veg)</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>6 hotels</t>
+          <t>0.5 hotels</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
@@ -6760,52 +6992,52 @@
       <c r="H40" s="3" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>Jun 13</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>Cold Mixed Lettuce → Lunch</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>3 bins</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr"/>
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Jun 12</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Pick up Baked Rolls at GC</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>GC → Rex</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>GC → Rex</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Jun 13</t>
+          <t>Jun 12</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -6815,12 +7047,12 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>HOT Beef Massaman Curry → Dinner</t>
+          <t>HOT Vegetable Biryani → Dinner</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>3 hotels</t>
+          <t>6 hotels</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
@@ -6838,78 +7070,78 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Jun 12</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Cold Tuna Rex Salad Mix → Sat Lunch</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>Jun 13</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>HOT Vegan Massaman Curry → Dinner (Veg)</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>0.5 hotels</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>Jun 13</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>HOT Rice → Dinner side</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Cold Mixed Lettuce → Lunch</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>3 bins</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -6929,25 +7161,139 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
+          <t>HOT Beef Massaman Curry → Dinner</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Jun 13</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>HOT Vegan Massaman Curry → Dinner (Veg)</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>0.5 hotels</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Jun 13</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>HOT Rice → Dinner side</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Jun 13</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
           <t>Cold Broccoli Salad → NC Wk1 Sun Lunch</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="E48" s="3" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
         <is>
           <t>fridge</t>
         </is>

--- a/outputs/03_Driver_Schedule_generated.xlsx
+++ b/outputs/03_Driver_Schedule_generated.xlsx
@@ -1443,7 +1443,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>No AM run — Bean Salad pre-sent Thu PM</t>
+          <t>Bean Salad at Rex — sent Thu PM</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>No AM run — Coronation Chicken Salad pre-sent Tue PM</t>
+          <t>Coronation Chicken Salad at Rex — sent Tue PM</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>No AM run — Tuna Rex + Chickpea Rex Salad pre-sent Fri PM</t>
+          <t>Tuna Rex + Chickpea Rex Salad at Rex — sent Fri PM</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>No AM run — Bean Salad pre-sent Thu PM</t>
+          <t>Bean Salad at Rex — sent Thu PM</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr"/>
@@ -6351,7 +6351,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>No AM run — Coronation Chicken Salad pre-sent Tue PM</t>
+          <t>Coronation Chicken Salad at Rex — sent Tue PM</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>

--- a/outputs/03_Driver_Schedule_generated.xlsx
+++ b/outputs/03_Driver_Schedule_generated.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1426,118 +1426,118 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>May 22</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Bean Salad at Rex — sent Thu PM</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Cold salad already at Rex</t>
-        </is>
-      </c>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>May 21</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Cold Pork Vindaloo → Rex fridge</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>40 lbs</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>May 21</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Cold Chicken Vindaloo — Halal → Rex fridge</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>32 lbs</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>May 22</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>Pick up Baked Rolls at GC</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>pickup</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>May 22</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>HOT Pork/Chicken/Halal + Veg Adobo → Dinner</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Bean Salad at Rex — sent Thu PM</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Cold salad already at Rex</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -1557,22 +1557,22 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>HOT Pineapple Rice → Dinner side</t>
+          <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>4 hotels</t>
+          <t>pickup</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr"/>
@@ -1595,177 +1595,177 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
+          <t>HOT Pork/Chicken/Halal + Veg Adobo → Dinner</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>May 22</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>HOT Pineapple Rice → Dinner side</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>May 22</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
           <t>HOT Green Beans → Dinner side</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>May 23</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>AM</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>HOT CONC Salad Beef → Lunch</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>2 hotels</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>May 23</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>AM</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>HOT CONC Salad Vegan → Lunch (Veg)</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>0.5 hotel</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>May 23</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>Pick up Baked Rolls at GC</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>pickup</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>May 23</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>HOT Gomen Besiga Beef → Dinner</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>80 lbs</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -1785,22 +1785,22 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>HOT Vegan Gomen Besiga → Dinner (Veg)</t>
+          <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>15 lbs</t>
+          <t>pickup</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr"/>
@@ -1823,22 +1823,22 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>HOT Carrot Cabbage Fry → Dinner side</t>
+          <t>HOT Gomen Besiga Beef → Dinner</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>2 hotels</t>
+          <t>80 lbs</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr"/>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>HOT Rice → Dinner</t>
+          <t>HOT Vegan Gomen Besiga → Dinner (Veg)</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>4 hotels</t>
+          <t>15 lbs</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -1899,25 +1899,101 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
+          <t>HOT Carrot Cabbage Fry → Dinner side</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>May 23</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>HOT Rice → Dinner</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>May 23</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
           <t>Cold Greens + Lettuce/Tomato → Sun Lunch</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="E40" s="3" t="inlineStr">
         <is>
           <t>3 bins + 1 bag</t>
         </is>
       </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
         <is>
           <t>fridge</t>
         </is>

--- a/outputs/03_Driver_Schedule_generated.xlsx
+++ b/outputs/03_Driver_Schedule_generated.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1194,194 +1194,194 @@
       <c r="H19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>May 21</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>HOT Halal Chicken Burgers → Lunch</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>185 pcs</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr"/>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>May 20</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Cold Pork Vindaloo → Rex fridge</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>40 lbs</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>May 21</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>HOT Quinoa Burgers → Lunch (Veg)</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>20 pcs</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr"/>
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>May 20</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Cold Chicken Vindaloo — Halal → Rex fridge</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>32 lbs</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>May 20</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>HOT Shakshuka Chicken Legs → Dinner</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>165 pcs</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>May 21</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Pick up Baked Rolls at GC</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>pickup</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>HOT Halal Chicken Burgers → Lunch</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>185 pcs</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>May 21</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>HOT Butter Chicken + Butter Chickpeas → Dinner</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>80+20 lbs</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>May 21</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>HOT Roasted Cauliflower → Dinner side</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>HOT Quinoa Burgers → Lunch (Veg)</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>20 pcs</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -1401,29 +1401,25 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>HOT Naan → Dinner</t>
+          <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>200 pcs</t>
+          <t>pickup</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>Purchased; delivered direct to Rex or via van</t>
-        </is>
-      </c>
+          <t>GC → Rex</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -1443,12 +1439,12 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Cold Pork Vindaloo → Rex fridge</t>
+          <t>HOT Butter Chicken + Butter Chickpeas → Dinner</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>40 lbs</t>
+          <t>80+20 lbs</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -1481,101 +1477,105 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Cold Chicken Vindaloo — Halal → Rex fridge</t>
+          <t>HOT Roasted Cauliflower → Dinner side</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>32 lbs</t>
+          <t>2 hotels</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>LAN → Rex</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>LAN → Rex</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>May 21</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>HOT Naan → Dinner</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>200 pcs</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Purchased; delivered direct to Rex or via van</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>May 22</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>AM</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Bean Salad at Rex — sent Thu PM</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Cold salad already at Rex</t>
         </is>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>May 22</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>Pick up Baked Rolls at GC</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>pickup</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -1595,22 +1595,22 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>HOT Pork/Chicken/Halal + Veg Adobo → Dinner</t>
+          <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>3 hotels</t>
+          <t>pickup</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr"/>
@@ -1692,194 +1692,194 @@
       <c r="H32" s="3" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>May 23</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>HOT CONC Salad Beef → Lunch</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr"/>
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>May 22</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>HOT Pork Adobo → Dinner</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>40 lbs</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>May 23</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>HOT CONC Salad Vegan → Lunch (Veg)</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>0.5 hotel</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr"/>
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>May 22</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>HOT Halal Chicken Adobo → Dinner (Halal)</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>32 lbs</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>May 22</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>HOT Adobo Tofu → Dinner (Veg)</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>0.5u</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>May 23</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>Pick up Baked Rolls at GC</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>pickup</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>HOT CONC Salad Beef → Lunch</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>May 23</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>HOT Gomen Besiga Beef → Dinner</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>80 lbs</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>May 23</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>HOT Vegan Gomen Besiga → Dinner (Veg)</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>15 lbs</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>HOT CONC Salad Vegan → Lunch (Veg)</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>0.5 hotel</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -1899,22 +1899,22 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>HOT Carrot Cabbage Fry → Dinner side</t>
+          <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>2 hotels</t>
+          <t>pickup</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr"/>
@@ -1937,12 +1937,12 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>HOT Rice → Dinner</t>
+          <t>HOT Gomen Besiga Beef → Dinner</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>4 hotels</t>
+          <t>80 lbs</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -1975,25 +1975,139 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
+          <t>HOT Vegan Gomen Besiga → Dinner (Veg)</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>15 lbs</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>May 23</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>HOT Carrot Cabbage Fry → Dinner side</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>May 23</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>HOT Rice → Dinner</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>May 23</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
           <t>Cold Greens + Lettuce/Tomato → Sun Lunch</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>3 bins + 1 bag</t>
         </is>
       </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
         <is>
           <t>fridge</t>
         </is>

--- a/outputs/03_Driver_Schedule_generated.xlsx
+++ b/outputs/03_Driver_Schedule_generated.xlsx
@@ -5628,7 +5628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6524,80 +6524,80 @@
       <c r="H23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Jun 9</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Cold Chickpea Shakshuka → Rex fridge (NC Wk1 Wed Dinner)</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>80 lbs</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Jun 10</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>AM</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Coronation Chicken Salad at Rex — sent Tue PM</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Cold salad already at Rex</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Jun 10</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>HOT Vegan Pot Pie + Veg Medley → Dinner (Veg)</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>30 lbs</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -6617,12 +6617,12 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>HOT Roasted Potatoes → Dinner</t>
+          <t>HOT Vegan Pot Pie + Veg Medley → Dinner (Veg)</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>4 hotels</t>
+          <t>30 lbs</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>HOT Eggplant/Cassava Stew → Dinner</t>
+          <t>HOT Roasted Potatoes → Dinner</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>2 hotels</t>
+          <t>4 hotels</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -6693,12 +6693,12 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>HOT Beef &amp; Vegetable Stew → Dinner</t>
+          <t>HOT Eggplant/Cassava Stew → Dinner</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>3 hotels</t>
+          <t>2 hotels</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -6731,63 +6731,63 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
+          <t>HOT Beef &amp; Vegetable Stew → Dinner</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Jun 10</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
           <t>Cold Chickpea Salad → Thu Lunch</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>2 bins</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Jun 11</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>HOT Halal Beef Burgers → Lunch</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr"/>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6807,12 +6807,12 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>HOT Black Bean Patties → Lunch (Veg)</t>
+          <t>HOT Halal Beef Burgers → Lunch</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>20 pcs</t>
+          <t>3 hotels</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6845,63 +6845,63 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>HOT Black Bean Patties → Lunch (Veg)</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>20 pcs</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Jun 11</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
           <t>Cold Lettuce / Tomato → Lunch</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>1 unit</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>Jun 11</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>HOT Teriyaki Chicken + Five-Spice Tofu → Dinner</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>215 pcs</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -6921,12 +6921,12 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>HOT Chow Mein + Nappa Cabbage → Dinner</t>
+          <t>HOT Teriyaki Chicken + Five-Spice Tofu → Dinner</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>8 hotels</t>
+          <t>215 pcs</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Cold Beef Nacho Mix → Rex fridge</t>
+          <t>HOT Chow Mein + Nappa Cabbage → Dinner</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>80 lbs</t>
+          <t>8 hotels</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -6977,11 +6977,7 @@
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>Rex holds until Wk1 Mon AM pull</t>
-        </is>
-      </c>
+      <c r="H35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -7001,12 +6997,12 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Cold Vegan Nacho Mix → Rex fridge</t>
+          <t>Cold Beef Nacho Mix → Rex fridge</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>15 lbs</t>
+          <t>80 lbs</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -7043,25 +7039,29 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Cold Chicken Ranch Mix → Fri Lunch</t>
+          <t>Cold Vegan Nacho Mix → Rex fridge</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>2 bins</t>
+          <t>15 lbs</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr"/>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Rex holds until Wk1 Mon AM pull</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -7081,105 +7081,105 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
+          <t>Cold Chicken Ranch Mix → Fri Lunch</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Jun 11</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
           <t>Cold Slaw → Fri Lunch side</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>2 bins</t>
         </is>
       </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
         <is>
           <t>⚠ CONFIRM 2 bins/4u — LAN → Rex</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>Jun 12</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>AM</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>HOT Crispy Falafel → Lunch (Veg)</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>0.5 hotel</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>Jun 12</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>HOT Tandoori Tofu → Dinner (Veg)</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>0.5 hotels</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -7199,22 +7199,22 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Pick up Baked Rolls at GC</t>
+          <t>HOT Tandoori Tofu → Dinner (Veg)</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>pickup</t>
+          <t>0.5 hotels</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>GC → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>GC → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr"/>
@@ -7237,22 +7237,22 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>HOT Vegetable Biryani → Dinner</t>
+          <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>6 hotels</t>
+          <t>pickup</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr"/>
@@ -7275,101 +7275,101 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
+          <t>HOT Vegetable Biryani → Dinner</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>6 hotels</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Jun 12</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
           <t>Cold Tuna Rex Salad Mix → Sat Lunch</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E44" s="3" t="inlineStr">
         <is>
           <t>2 bins</t>
         </is>
       </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>Jun 13</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>AM</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Cold Mixed Lettuce → Lunch</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>3 bins</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>Jun 13</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>HOT Beef Massaman Curry → Dinner</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>HOT Vegan Massaman Curry → Dinner (Veg)</t>
+          <t>HOT Beef Massaman Curry → Dinner</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>0.5 hotels</t>
+          <t>3 hotels</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>HOT Rice → Dinner side</t>
+          <t>HOT Vegan Massaman Curry → Dinner (Veg)</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>4 hotels</t>
+          <t>0.5 hotels</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
@@ -7465,25 +7465,63 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
+          <t>HOT Rice → Dinner side</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Jun 13</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
           <t>Cold Broccoli Salad → NC Wk1 Sun Lunch</t>
         </is>
       </c>
-      <c r="E48" s="3" t="inlineStr">
+      <c r="E49" s="3" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="F48" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G48" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
         <is>
           <t>fridge</t>
         </is>

--- a/outputs/03_Driver_Schedule_generated.xlsx
+++ b/outputs/03_Driver_Schedule_generated.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1540,118 +1540,118 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>May 22</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Bean Salad at Rex — sent Thu PM</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr"/>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>Cold salad already at Rex</t>
-        </is>
-      </c>
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>May 21</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Cold Egg Salad Mix → Rex fridge (Fri Lunch)</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>May 21</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Cold Bean Salad → Rex fridge (Fri Lunch)</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>May 22</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>Pick up Baked Rolls at GC</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>pickup</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>May 22</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>HOT Pineapple Rice → Dinner side</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Egg Salad Wrap + Bean Salad at Rex — sent Thu PM</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Cold salad already at Rex</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -1671,22 +1671,22 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>HOT Green Beans → Dinner side</t>
+          <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>3 hotels</t>
+          <t>pickup</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr"/>
@@ -1709,22 +1709,22 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>HOT Pork Adobo → Dinner</t>
+          <t>HOT Pineapple Rice → Dinner side</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>40 lbs</t>
+          <t>4 hotels</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>LAN → Rex</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>LAN → Rex</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr"/>
@@ -1747,12 +1747,12 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>HOT Halal Chicken Adobo → Dinner (Halal)</t>
+          <t>HOT Green Beans → Dinner side</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>32 lbs</t>
+          <t>3 hotels</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -1785,177 +1785,177 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
+          <t>HOT Pork Adobo → Dinner</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>40 lbs</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>May 22</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>HOT Halal Chicken Adobo → Dinner (Halal)</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>32 lbs</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>May 22</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
           <t>HOT Adobo Tofu → Dinner (Veg)</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>0.5u</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>May 23</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>AM</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>HOT CONC Salad Beef → Lunch</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>2 hotels</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>May 23</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>AM</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>HOT CONC Salad Vegan → Lunch (Veg)</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>0.5 hotel</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>May 23</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>Pick up Baked Rolls at GC</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>pickup</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>May 23</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>HOT Gomen Besiga Beef → Dinner</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>80 lbs</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -1975,22 +1975,22 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>HOT Vegan Gomen Besiga → Dinner (Veg)</t>
+          <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>15 lbs</t>
+          <t>pickup</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr"/>
@@ -2013,22 +2013,22 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>HOT Carrot Cabbage Fry → Dinner side</t>
+          <t>HOT Gomen Besiga Beef → Dinner</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>2 hotels</t>
+          <t>80 lbs</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr"/>
@@ -2051,12 +2051,12 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>HOT Rice → Dinner</t>
+          <t>HOT Vegan Gomen Besiga → Dinner (Veg)</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>4 hotels</t>
+          <t>15 lbs</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
@@ -2089,25 +2089,101 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
+          <t>HOT Carrot Cabbage Fry → Dinner side</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>May 23</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>HOT Rice → Dinner</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>May 23</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
           <t>Cold Greens + Lettuce/Tomato → Sun Lunch</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr">
         <is>
           <t>3 bins + 1 bag</t>
         </is>
       </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
         <is>
           <t>fridge</t>
         </is>
@@ -3840,7 +3916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5205,7 +5281,7 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Cold Egg Salad + Bean Salad → Fri Lunch</t>
+          <t>Cold Egg Salad Mix → Rex fridge (Fri Lunch)</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -5230,80 +5306,80 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Jun 4</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Cold Bean Salad → Rex fridge (Fri Lunch)</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>Jun 5</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>AM</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>Bean Salad at Rex — sent Thu PM</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr"/>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Egg Salad Wrap + Bean Salad at Rex — sent Thu PM</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Cold salad already at Rex</t>
         </is>
       </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>Jun 5</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>HOT Chicken &amp; Mushroom Fried Rice → Dinner</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>5 hotels</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -5323,12 +5399,12 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>HOT Vegan/No-Soy Mushroom Fried Rice → Dinner (Veg)</t>
+          <t>HOT Chicken &amp; Mushroom Fried Rice → Dinner</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>1 hotel</t>
+          <t>5 hotels</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -5361,63 +5437,63 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
+          <t>HOT Vegan/No-Soy Mushroom Fried Rice → Dinner (Veg)</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Jun 5</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
           <t>HOT Spring Rolls → Dinner side</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t>2 hotels</t>
         </is>
       </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>Jun 6</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>HOT CONC Salad Beef → Lunch</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>80 lbs</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr"/>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -5437,63 +5513,63 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
+          <t>HOT CONC Salad Beef → Lunch</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>80 lbs</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Jun 6</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
           <t>HOT CONC Salad Vegan → Lunch (Veg)</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>12 lbs</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Jun 6</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>Pick up Baked Rolls at GC</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>pickup</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -5513,7 +5589,7 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Pick up Pepperoni + Veg Pizza at vendor</t>
+          <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -5523,19 +5599,15 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Vendor → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>Vendor → Rex</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>Driver collects ordered pizza</t>
-        </is>
-      </c>
+          <t>GC → Rex</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -5555,27 +5627,27 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Cold Greens + Lettuce/Tomato → Sun Lunch</t>
+          <t>Pick up Pepperoni + Veg Pizza at vendor</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>3 bins + 1 bag</t>
+          <t>pickup</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Vendor → Rex</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Vendor → Rex</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>fridge</t>
+          <t>Driver collects ordered pizza</t>
         </is>
       </c>
     </row>
@@ -5597,25 +5669,67 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
+          <t>Cold Greens + Lettuce/Tomato → Sun Lunch</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>3 bins + 1 bag</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>fridge</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Jun 6</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
           <t>HOT Potato Wedges → Dinner</t>
         </is>
       </c>
-      <c r="E46" s="3" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr"/>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/03_Driver_Schedule_generated.xlsx
+++ b/outputs/03_Driver_Schedule_generated.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -624,80 +624,76 @@
       <c r="H4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>May 17</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>HOT Vegan Mushroom Stroganoff → Dinner (Veg)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>May 18</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>AM</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>HOT Falafels → Lunch (Veg)</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>2 hotels</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>May 18</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Pick up Baked Rolls at GC</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>pickup</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -717,22 +713,22 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>HOT Jerk Chicken → Dinner</t>
+          <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>1.5 hotels</t>
+          <t>pickup</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr"/>
@@ -755,177 +751,177 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
+          <t>HOT Jerk Chicken → Dinner</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>1.5 hotels</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>May 18</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
           <t>HOT Rice &amp; Beans → Dinner</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>May 18</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>HOT Cabbage &amp; Carrot Stir-fry → Dinner side</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>3 bins</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>May 19</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>AM</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>HOT Beef Nacho Mix → Lunch</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>2 hotels</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>May 19</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>AM</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>HOT Vegan Nacho Mix → Lunch (Veg)</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>0.5 hotels</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>May 19</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Pick up Baked Rolls at GC</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>pickup</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>May 19</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>HOT Pork/Chicken/Halal Carnitas → Dinner</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -945,101 +941,101 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
+          <t>Pick up Baked Rolls at GC</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>GC → Rex</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>GC → Rex</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>May 19</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>HOT Pork/Chicken/Halal Carnitas → Dinner</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>May 19</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
           <t>HOT Broccoli → Dinner</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>May 20</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>HOT Crispy Chicken Tenders → Lunch</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>May 20</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>HOT Vegan Tenders → Lunch (Veg)</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>0.5 hotels</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1059,101 +1055,101 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>HOT Crispy Chicken Tenders → Lunch</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>May 20</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>HOT Vegan Tenders → Lunch (Veg)</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0.5 hotels</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>May 20</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>Cold Chiffonade Lettuce &amp; Sliced Peppers → Lunch (wraps)</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>1 hotel</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>May 20</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Pick up Baked Rolls at GC</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>pickup</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>May 20</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>HOT Shakshuka Sauce → Dinner</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>80 lbs</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -1173,22 +1169,22 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>HOT Herbed Couscous → Dinner side</t>
+          <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>4 hotels</t>
+          <t>pickup</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr"/>
@@ -1211,12 +1207,12 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Cold Pork Vindaloo → Rex fridge</t>
+          <t>HOT Shakshuka Sauce → Dinner</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>40 lbs</t>
+          <t>80 lbs</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -1249,22 +1245,22 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Cold Chicken Vindaloo — Halal → Rex fridge</t>
+          <t>HOT Herbed Couscous → Dinner side</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>32 lbs</t>
+          <t>4 hotels</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>LAN → Rex</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>LAN → Rex</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr"/>
@@ -1287,177 +1283,177 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
+          <t>Cold Pork Vindaloo → Rex fridge</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>40 lbs</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>May 20</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Cold Chicken Vindaloo — Halal → Rex fridge</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>32 lbs</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>May 20</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
           <t>HOT Shakshuka Chicken Legs → Dinner</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>165 pcs</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>May 21</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>AM</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>HOT Halal Chicken Burgers → Lunch</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>185 pcs</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>May 21</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>AM</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>HOT Quinoa Burgers → Lunch (Veg)</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>20 pcs</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>May 21</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>Pick up Baked Rolls at GC</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>pickup</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>May 21</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>HOT Butter Chicken + Butter Chickpeas → Dinner</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>80+20 lbs</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -1477,22 +1473,22 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>HOT Roasted Cauliflower → Dinner side</t>
+          <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>2 hotels</t>
+          <t>pickup</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr"/>
@@ -1515,12 +1511,12 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>HOT Naan → Dinner</t>
+          <t>HOT Butter Chicken + Butter Chickpeas → Dinner</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>200 pcs</t>
+          <t>80+20 lbs</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -1533,11 +1529,7 @@
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>Purchased; delivered direct to Rex or via van</t>
-        </is>
-      </c>
+      <c r="H28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -1557,12 +1549,12 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Cold Egg Salad Mix → Rex fridge (Fri Lunch)</t>
+          <t>HOT Roasted Cauliflower → Dinner side</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>2 bins</t>
+          <t>2 hotels</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -1595,139 +1587,143 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Cold Bean Salad → Rex fridge (Fri Lunch)</t>
+          <t>HOT Naan → Dinner</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
+          <t>200 pcs</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Purchased; delivered direct to Rex or via van</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>May 21</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Cold Egg Salad Mix → Rex fridge (Fri Lunch)</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
           <t>2 bins</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>May 22</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Egg Salad Wrap + Bean Salad at Rex — sent Thu PM</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr"/>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>Cold salad already at Rex</t>
-        </is>
-      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>May 21</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Cold Bean Salad → Rex fridge (Fri Lunch)</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>May 22</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>Pick up Baked Rolls at GC</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>pickup</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>May 22</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>HOT Pineapple Rice → Dinner side</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Egg Salad Wrap + Bean Salad at Rex — sent Thu PM</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Cold salad already at Rex</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -1747,22 +1743,22 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>HOT Green Beans → Dinner side</t>
+          <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>3 hotels</t>
+          <t>pickup</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr"/>
@@ -1785,22 +1781,22 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>HOT Pork Adobo → Dinner</t>
+          <t>HOT Pineapple Rice → Dinner side</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>40 lbs</t>
+          <t>4 hotels</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>LAN → Rex</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>LAN → Rex</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr"/>
@@ -1823,12 +1819,12 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>HOT Halal Chicken Adobo → Dinner (Halal)</t>
+          <t>HOT Green Beans → Dinner side</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>32 lbs</t>
+          <t>3 hotels</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -1861,177 +1857,177 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
+          <t>HOT Pork Adobo → Dinner</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>40 lbs</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>May 22</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>HOT Halal Chicken Adobo → Dinner (Halal)</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>32 lbs</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>May 22</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
           <t>HOT Adobo Tofu → Dinner (Veg)</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>0.5u</t>
         </is>
       </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>May 23</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>AM</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>HOT CONC Salad Beef → Lunch</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>2 hotels</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>May 23</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>AM</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>HOT CONC Salad Vegan → Lunch (Veg)</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>0.5 hotel</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>May 23</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>Pick up Baked Rolls at GC</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>pickup</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>May 23</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>HOT Gomen Besiga Beef → Dinner</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>80 lbs</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -2051,22 +2047,22 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>HOT Vegan Gomen Besiga → Dinner (Veg)</t>
+          <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>15 lbs</t>
+          <t>pickup</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr"/>
@@ -2089,22 +2085,22 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>HOT Carrot Cabbage Fry → Dinner side</t>
+          <t>HOT Gomen Besiga Beef → Dinner</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>2 hotels</t>
+          <t>80 lbs</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr"/>
@@ -2127,12 +2123,12 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>HOT Rice → Dinner</t>
+          <t>HOT Vegan Gomen Besiga → Dinner (Veg)</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>4 hotels</t>
+          <t>15 lbs</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
@@ -2165,27 +2161,145 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
+          <t>HOT Carrot Cabbage Fry → Dinner side</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>May 23</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>HOT Rice → Dinner</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>May 23</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
           <t>Cold Greens + Lettuce/Tomato → Sun Lunch</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>3 bins + 1 bag</t>
         </is>
       </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
         <is>
           <t>fridge</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>May 23</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>HOT BLAND ALT → Dinner</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>2 pcs</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Small batch ALT</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2568,42 +2682,46 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>May 25</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Pick up Baked Rolls at GC</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>pickup</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>HOT BLAND ALT Chicken → Lunch</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3 pcs</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Small batch ALT</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2623,22 +2741,22 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>HOT Peanut Chicken Stew → Dinner</t>
+          <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>80 lbs</t>
+          <t>pickup</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr"/>
@@ -2661,12 +2779,12 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>HOT Vegan Peanut Stew → Dinner (Veg)</t>
+          <t>HOT Peanut Chicken Stew → Dinner</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>12 lbs</t>
+          <t>80 lbs</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -2699,12 +2817,12 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>HOT Rice → Dinner</t>
+          <t>HOT Vegan Peanut Stew → Dinner (Veg)</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>4 hotels</t>
+          <t>12 lbs</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -2737,139 +2855,139 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
+          <t>HOT Rice → Dinner</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>May 25</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
           <t>HOT Green Beans → Dinner side</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>May 26</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>AM</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>HOT Beef/Halal Sausages → Lunch</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>200 pcs</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>May 26</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>HOT Pork/Chicken/Halal + Veg Vindaloo → Dinner</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>85+15 lbs</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>May 26</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>HOT Steamed Rice → Dinner</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr"/>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>HOT Roasted Peppers &amp; Onions → Lunch</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -2889,22 +3007,22 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>HOT Broccoli → Dinner side</t>
+          <t>HOT Pork/Chicken/Halal + Veg Vindaloo → Dinner</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>3 hotels</t>
+          <t>85+15 lbs</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr"/>
@@ -2927,73 +3045,73 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Cold Coronation Chicken Salad → Wed Lunch</t>
+          <t>HOT Steamed Rice → Dinner</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>2 bins</t>
+          <t>4 hotels</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>May 27</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Coronation Chicken Salad at Rex — sent Tue PM</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Cold salad already at Rex</t>
-        </is>
-      </c>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>May 26</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>HOT Broccoli → Dinner side</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>May 27</t>
+          <t>May 26</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -3003,22 +3121,22 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Pick up Baked Rolls at GC</t>
+          <t>Cold Coronation Chicken Salad → Wed Lunch</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>pickup</t>
+          <t>2 bins</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>GC → Rex</t>
+          <t>LAN → Rex</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>GC → Rex</t>
+          <t>LAN → Rex</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr"/>
@@ -3026,116 +3144,124 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>May 26</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>HOT BLAND ALT → Dinner</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>3 pcs</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Small batch ALT</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>May 27</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>HOT Yetisse Fish → Dinner</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>150 pcs</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Coronation Chicken Salad at Rex — sent Tue PM</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Cold salad already at Rex</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>May 27</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>HOT Spiced Tofu → Dinner (Veg)</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>50 pcs</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>May 27</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>HOT Coconut Rice &amp; Peas → Dinner</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>HOT GF ALT Roasted Potatoes → Lunch</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>small batch</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>GF alternative</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -3155,22 +3281,22 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>HOT Eggplant/Cassava Stew → Dinner</t>
+          <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>2 hotels</t>
+          <t>pickup</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr"/>
@@ -3193,12 +3319,12 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Cold Chickpea Salad → Thu Lunch</t>
+          <t>HOT Yetisse Fish → Dinner</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>2 bins</t>
+          <t>150 pcs</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -3214,90 +3340,90 @@
       <c r="H26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>May 28</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>HOT Halal Beef Burgers → Lunch</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>160 pcs</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr"/>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>May 27</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>HOT Spiced Tofu → Dinner (Veg)</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>50 pcs</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>May 28</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>HOT Black Bean Patties → Lunch (Veg)</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>20 pcs</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr"/>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>May 27</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>HOT Coconut Rice &amp; Peas → Dinner</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>May 28</t>
+          <t>May 27</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -3307,12 +3433,12 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>HOT Beef/Halal/Vegan Sausages → Dinner</t>
+          <t>HOT Eggplant/Cassava Stew → Dinner</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>250 pcs</t>
+          <t>2 hotels</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -3330,116 +3456,116 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>May 27</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Cold Chickpea Salad → Thu Lunch</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>May 28</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>HOT Mashed Potato → Dinner</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>80 lbs</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>HOT Halal Beef Burgers → Lunch</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>160 pcs</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>May 28</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>HOT Peas &amp; Carrot → Dinner side</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>May 28</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>HOT Gravy → Dinner</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>½ batch</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>HOT Black Bean Patties → Lunch (Veg)</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>20 pcs</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -3459,22 +3585,22 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Cold Chicken Ranch Mix → Fri Lunch</t>
+          <t>HOT Beef/Halal/Vegan Sausages → Dinner</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>2 bins</t>
+          <t>250 pcs</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr"/>
@@ -3497,73 +3623,73 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Cold Slaw → Fri Lunch side</t>
+          <t>HOT Mashed Potato → Dinner</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>2 bins</t>
+          <t>80 lbs</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>May 29</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>HOT Crispy Falafel → Lunch (Veg)</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>0.5 hotel</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr"/>
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>May 28</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>HOT Peas &amp; Carrot → Dinner side</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>May 29</t>
+          <t>May 28</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -3573,12 +3699,12 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>HOT Arroz con Pollo + Vegan Arroz → Dinner</t>
+          <t>HOT Gravy → Dinner</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>100 lbs</t>
+          <t>½ batch</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -3596,12 +3722,12 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>May 29</t>
+          <t>May 28</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -3611,22 +3737,22 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>HOT Refried Beans → Dinner side</t>
+          <t>Cold Chicken Ranch Mix → Fri Lunch</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>3 hotels</t>
+          <t>2 bins</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>LAN → Rex</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>LAN → Rex</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr"/>
@@ -3634,12 +3760,12 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>May 29</t>
+          <t>May 28</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -3649,7 +3775,7 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Cold Tuna Rex Salad Mix → Sat Lunch</t>
+          <t>Cold Slaw → Fri Lunch side</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -3672,12 +3798,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>May 30</t>
+          <t>May 29</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3687,10 +3813,14 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Tuna Rex + Chickpea Rex Salad at Rex — sent Fri PM</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr"/>
+          <t>HOT Crispy Falafel → Lunch (Veg)</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>0.5 hotel</t>
+        </is>
+      </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
@@ -3701,21 +3831,17 @@
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>Cold salad already at Rex</t>
-        </is>
-      </c>
+      <c r="H39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>May 30</t>
+          <t>May 29</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -3725,22 +3851,22 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>HOT Beef + Vegan Meatloaf → Dinner</t>
+          <t>HOT Arroz con Pollo + Vegan Arroz → Dinner</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>8 trays</t>
+          <t>100 lbs</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr"/>
@@ -3748,12 +3874,12 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>May 30</t>
+          <t>May 29</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -3763,22 +3889,22 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>HOT Roasted Potatoes → Dinner</t>
+          <t>HOT Refried Beans → Dinner side</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>4 hotels</t>
+          <t>3 hotels</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr"/>
@@ -3786,80 +3912,76 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>May 29</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Cold Tuna Rex Salad Mix → Sat Lunch</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>May 30</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>HOT Butternut Squash → Dinner side</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>May 30</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>HOT Gravy → Dinner (Meatloaf)</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>½ batch</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>Held from Thu batch</t>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Tuna Rex + Chickpea Rex Salad at Rex — sent Fri PM</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Cold salad already at Rex</t>
         </is>
       </c>
     </row>
@@ -3881,25 +4003,181 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
+          <t>HOT Beef + Vegan Meatloaf → Dinner</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>8 trays</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>May 30</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>HOT Roasted Potatoes → Dinner</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>May 30</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>HOT Butternut Squash → Dinner side</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>May 30</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>HOT Gravy → Dinner (Meatloaf)</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>½ batch</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>Held from Thu batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>May 30</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
           <t>Cold Broccoli Salad → Wk3 Sun Lunch</t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr">
+      <c r="E48" s="3" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
         <is>
           <t>fridge</t>
         </is>
@@ -3916,7 +4194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5496,42 +5774,38 @@
       <c r="H41" s="3" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Jun 6</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>HOT CONC Salad Beef → Lunch</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>80 lbs</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr"/>
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Jun 5</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>HOT Bok Choy → Dinner side</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr"/>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -5551,63 +5825,63 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
+          <t>HOT CONC Salad Beef → Lunch</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>80 lbs</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Jun 6</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
           <t>HOT CONC Salad Vegan → Lunch (Veg)</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>12 lbs</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>Jun 6</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>Pick up Baked Rolls at GC</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>pickup</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -5627,7 +5901,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Pick up Pepperoni + Veg Pizza at vendor</t>
+          <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -5637,19 +5911,15 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>Vendor → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>Vendor → Rex</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>Driver collects ordered pizza</t>
-        </is>
-      </c>
+          <t>GC → Rex</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -5669,27 +5939,27 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Cold Greens + Lettuce/Tomato → Sun Lunch</t>
+          <t>Pick up Pepperoni + Veg Pizza at vendor</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>3 bins + 1 bag</t>
+          <t>pickup</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Vendor → Rex</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Vendor → Rex</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>fridge</t>
+          <t>Driver collects ordered pizza</t>
         </is>
       </c>
     </row>
@@ -5711,25 +5981,67 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
+          <t>Cold Greens + Lettuce/Tomato → Sun Lunch</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>3 bins + 1 bag</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>fridge</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Jun 6</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
           <t>HOT Potato Wedges → Dinner</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr">
+      <c r="E48" s="3" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr"/>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5742,7 +6054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6106,42 +6418,46 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Jun 8</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>HOT Curry Fish → Dinner</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>HOT BLAND ALT Chicken → Lunch</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3 pcs</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Small batch ALT</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -6161,12 +6477,12 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>HOT Curry Spiced Tofu → Dinner (Veg)</t>
+          <t>HOT Curry Fish → Dinner</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>0.5 hotels</t>
+          <t>4 hotels</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -6199,12 +6515,12 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>HOT Green Curry Sauce → Dinner</t>
+          <t>HOT Curry Spiced Tofu → Dinner (Veg)</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>2 hotels</t>
+          <t>0.5 hotels</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -6237,101 +6553,105 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
+          <t>HOT Green Curry Sauce → Dinner</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Jun 8</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
           <t>HOT Rice + Green Beans → Dinner</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>7 hotels</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Jun 9</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>HOT Beef/Halal Sausages → Lunch</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>155 pcs</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Jun 9</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>HOT Vegan Sausages → Lunch (Veg)</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>15 pcs</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr"/>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Jun 8</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>HOT BLAND ALT Fish → Dinner</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>2 pcs</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Small batch ALT (no onion)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -6351,12 +6671,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>HOT Crispy Quinoa Cakes → Lunch (Veg alt)</t>
+          <t>HOT Beef/Halal Sausages → Lunch</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25 pcs</t>
+          <t>155 pcs</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -6389,22 +6709,22 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>HOT Roasted Peppers &amp; Onions → Lunch</t>
+          <t>HOT Vegan Sausages → Lunch (Veg)</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1 hotel</t>
+          <t>15 pcs</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr"/>
@@ -6427,101 +6747,101 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>HOT Crispy Quinoa Cakes → Lunch (Veg alt)</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>25 pcs</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Jun 9</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>HOT Roasted Peppers &amp; Onions → Lunch</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Jun 9</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
           <t>Cold Mixed Greens → Lunch side</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>3 bins</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Jun 9</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>HOT BBQ Chicken Legs → Dinner</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>1 hotel</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Jun 9</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>HOT BBQ Vegan Tenders → Dinner (Veg)</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>0.5 hotels</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -6541,12 +6861,12 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>HOT Herb Garlic Potatoes → Dinner</t>
+          <t>HOT BBQ Chicken Legs → Dinner</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>3 hotels</t>
+          <t>1 hotel</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -6579,22 +6899,22 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>HOT Peas &amp; Carrot → Dinner side</t>
+          <t>HOT BBQ Vegan Tenders → Dinner (Veg)</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>3 hotels</t>
+          <t>0.5 hotels</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr"/>
@@ -6617,22 +6937,22 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Cold Coronation Chicken Salad → Wed Lunch</t>
+          <t>HOT Herb Garlic Potatoes → Dinner</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>2 bins</t>
+          <t>3 hotels</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr"/>
@@ -6655,139 +6975,139 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Cold Chickpea Shakshuka → Rex fridge (NC Wk1 Wed Dinner)</t>
+          <t>HOT Peas &amp; Carrot → Dinner side</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>80 lbs</t>
+          <t>3 hotels</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>LAN → Rex</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>LAN → Rex</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Jun 10</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Coronation Chicken Salad at Rex — sent Tue PM</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr"/>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>Cold salad already at Rex</t>
-        </is>
-      </c>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Jun 9</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Cold Coronation Chicken Salad → Wed Lunch</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Jun 9</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Cold Chickpea Shakshuka → Rex fridge (NC Wk1 Wed Dinner)</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>80 lbs</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Jun 10</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>HOT Vegan Pot Pie + Veg Medley → Dinner (Veg)</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>30 lbs</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Jun 10</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>HOT Roasted Potatoes → Dinner</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Coronation Chicken Salad at Rex — sent Tue PM</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Cold salad already at Rex</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -6807,12 +7127,12 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>HOT Eggplant/Cassava Stew → Dinner</t>
+          <t>HOT Vegan Pot Pie + Veg Medley → Dinner (Veg)</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>2 hotels</t>
+          <t>30 lbs</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -6845,12 +7165,12 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>HOT Beef &amp; Vegetable Stew → Dinner</t>
+          <t>HOT Roasted Potatoes → Dinner</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>3 hotels</t>
+          <t>4 hotels</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -6883,101 +7203,101 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
+          <t>HOT Eggplant/Cassava Stew → Dinner</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Jun 10</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>HOT Beef &amp; Vegetable Stew → Dinner</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Jun 10</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
           <t>Cold Chickpea Salad → Thu Lunch</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>2 bins</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Jun 11</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>HOT Halal Beef Burgers → Lunch</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Jun 11</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>HOT Black Bean Patties → Lunch (Veg)</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>20 pcs</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr"/>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6997,101 +7317,101 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>HOT Halal Beef Burgers → Lunch</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Jun 11</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>HOT Black Bean Patties → Lunch (Veg)</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>20 pcs</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Jun 11</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
           <t>Cold Lettuce / Tomato → Lunch</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>1 unit</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Jun 11</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>HOT Teriyaki Chicken + Five-Spice Tofu → Dinner</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>215 pcs</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>Jun 11</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>HOT Chow Mein + Nappa Cabbage → Dinner</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>8 hotels</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -7111,12 +7431,12 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Cold Beef Nacho Mix → Rex fridge</t>
+          <t>HOT Teriyaki Chicken + Five-Spice Tofu → Dinner</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>80 lbs</t>
+          <t>215 pcs</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -7129,11 +7449,7 @@
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>Rex holds until Wk1 Mon AM pull</t>
-        </is>
-      </c>
+      <c r="H36" s="3" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -7153,12 +7469,12 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Cold Vegan Nacho Mix → Rex fridge</t>
+          <t>HOT Chow Mein + Nappa Cabbage → Dinner</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>15 lbs</t>
+          <t>8 hotels</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -7171,11 +7487,7 @@
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>Rex holds until Wk1 Mon AM pull</t>
-        </is>
-      </c>
+      <c r="H37" s="3" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -7195,25 +7507,29 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Cold Chicken Ranch Mix → Fri Lunch</t>
+          <t>Cold Beef Nacho Mix → Rex fridge</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>2 bins</t>
+          <t>80 lbs</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr"/>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Rex holds until Wk1 Mon AM pull</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -7233,143 +7549,147 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Cold Slaw → Fri Lunch side</t>
+          <t>Cold Vegan Nacho Mix → Rex fridge</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
+          <t>15 lbs</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Rex holds until Wk1 Mon AM pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Jun 11</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Cold Chicken Ranch Mix → Fri Lunch</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
           <t>2 bins</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>⚠ CONFIRM 2 bins/4u — LAN → Rex</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>Jun 12</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>HOT Crispy Falafel → Lunch (Veg)</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>0.5 hotel</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr"/>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Jun 11</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Cold Slaw → Fri Lunch side</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>⚠ CONFIRM 2 bins/4u — LAN → Rex</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Jun 12</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>HOT Tandoori Tofu → Dinner (Veg)</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>0.5 hotels</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Jun 12</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>Pick up Baked Rolls at GC</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>pickup</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>HOT Crispy Falafel → Lunch (Veg)</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>0.5 hotel</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -7389,12 +7709,12 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>HOT Vegetable Biryani → Dinner</t>
+          <t>HOT Tandoori Tofu → Dinner (Veg)</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>6 hotels</t>
+          <t>0.5 hotels</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
@@ -7427,139 +7747,139 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Cold Tuna Rex Salad Mix → Sat Lunch</t>
+          <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>2 bins</t>
+          <t>pickup</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>Jun 13</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>Cold Mixed Lettuce → Lunch</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>3 bins</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr"/>
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Jun 12</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>HOT Vegetable Biryani → Dinner</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>6 hotels</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Jun 12</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Cold Tuna Rex Salad Mix → Sat Lunch</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>Jun 13</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>HOT Beef Massaman Curry → Dinner</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>Jun 13</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>HOT Vegan Massaman Curry → Dinner (Veg)</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>0.5 hotels</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Cold Mixed Lettuce → Lunch</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>3 bins</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -7579,12 +7899,12 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>HOT Rice → Dinner side</t>
+          <t>HOT Beef Massaman Curry → Dinner</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>4 hotels</t>
+          <t>3 hotels</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
@@ -7617,27 +7937,145 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
+          <t>HOT Vegan Massaman Curry → Dinner (Veg)</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>0.5 hotels</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Jun 13</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>HOT Rice → Dinner side</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Jun 13</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
           <t>Cold Broccoli Salad → NC Wk1 Sun Lunch</t>
         </is>
       </c>
-      <c r="E49" s="3" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr">
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
         <is>
           <t>fridge</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Jun 13</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>HOT BLAND ALT → Dinner</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>3 pcs</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Small batch ALT</t>
         </is>
       </c>
     </row>
